--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.89991453941753</v>
+        <v>7.946236112655349</v>
       </c>
       <c r="D2" t="n">
-        <v>48.6569269407682</v>
+        <v>7.906750627874833</v>
       </c>
       <c r="E2" t="n">
-        <v>12.54773614888741</v>
+        <v>2.039007124194204</v>
       </c>
       <c r="F2" t="n">
-        <v>12.696060372271</v>
+        <v>2.063109810494037</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.57927620185608</v>
+        <v>6.269132382801613</v>
       </c>
       <c r="D3" t="n">
-        <v>38.34281054276504</v>
+        <v>6.230706713199319</v>
       </c>
       <c r="E3" t="n">
-        <v>12.54773614888741</v>
+        <v>2.039007124194204</v>
       </c>
       <c r="F3" t="n">
-        <v>12.696060372271</v>
+        <v>2.063109810494037</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.98432947836956</v>
+        <v>6.497453540235053</v>
       </c>
       <c r="D4" t="n">
-        <v>39.88416406465474</v>
+        <v>6.481176660506396</v>
       </c>
       <c r="E4" t="n">
-        <v>12.54773614888741</v>
+        <v>2.039007124194204</v>
       </c>
       <c r="F4" t="n">
-        <v>12.696060372271</v>
+        <v>2.063109810494037</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.00024693602749</v>
+        <v>7.637540127104467</v>
       </c>
       <c r="D5" t="n">
-        <v>47.00785805996667</v>
+        <v>7.638776934744583</v>
       </c>
       <c r="E5" t="n">
-        <v>12.54773614888741</v>
+        <v>2.039007124194204</v>
       </c>
       <c r="F5" t="n">
-        <v>12.696060372271</v>
+        <v>2.063109810494037</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.05232161201636</v>
+        <v>6.671002261952658</v>
       </c>
       <c r="D6" t="n">
-        <v>39.06472501827205</v>
+        <v>6.348017815469208</v>
       </c>
       <c r="E6" t="n">
-        <v>12.54773614888741</v>
+        <v>2.039007124194204</v>
       </c>
       <c r="F6" t="n">
-        <v>12.696060372271</v>
+        <v>2.063109810494037</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.38861317723811</v>
+        <v>3.638149641301193</v>
       </c>
       <c r="D7" t="n">
-        <v>19.71430827133643</v>
+        <v>3.203575094092169</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54773614888741</v>
+        <v>2.039007124194204</v>
       </c>
       <c r="F7" t="n">
-        <v>12.696060372271</v>
+        <v>2.063109810494037</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.315896253387097</v>
+        <v>1.513833141175403</v>
       </c>
       <c r="D8" t="n">
-        <v>9.813233933359699</v>
+        <v>1.594650514170951</v>
       </c>
       <c r="E8" t="n">
-        <v>12.54773614888741</v>
+        <v>2.039007124194204</v>
       </c>
       <c r="F8" t="n">
-        <v>12.696060372271</v>
+        <v>2.063109810494037</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.45687948414086</v>
+        <v>4.786742916172891</v>
       </c>
       <c r="D9" t="n">
-        <v>27.86696265920856</v>
+        <v>4.528381432121392</v>
       </c>
       <c r="E9" t="n">
-        <v>12.54773614888741</v>
+        <v>2.039007124194204</v>
       </c>
       <c r="F9" t="n">
-        <v>12.696060372271</v>
+        <v>2.063109810494037</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
